--- a/results/summary_results.xlsx
+++ b/results/summary_results.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KPIs Multimodal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KPI_nearest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Improve_nearest" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="KPI_centralized" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Improve_centralized" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,347 +416,1499 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>traffic_condition</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>avg_time_min</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total_distance_km</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>avg_distance_km</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_cost_vnd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>avg_cost_vnd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total_co2_kg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>avg_co2_kg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>delivery_count</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>multimodal_used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Full Multimodal</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="D2" t="n">
+        <v>587.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1761606.11</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5891.66</v>
+      </c>
+      <c r="H2" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J2" t="n">
+        <v>299</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Road + Metro</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="D3" t="n">
+        <v>587.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1761606.11</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5891.66</v>
+      </c>
+      <c r="H3" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J3" t="n">
+        <v>299</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Road + Waterbus</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="D4" t="n">
+        <v>587.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1761606.11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5891.66</v>
+      </c>
+      <c r="H4" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J4" t="n">
+        <v>299</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Road Only</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="D5" t="n">
+        <v>587.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1761606.11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5891.66</v>
+      </c>
+      <c r="H5" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J5" t="n">
+        <v>299</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Full Multimodal</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="D6" t="n">
+        <v>587.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1761606.11</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5891.66</v>
+      </c>
+      <c r="H6" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J6" t="n">
+        <v>299</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Road + Metro</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="D7" t="n">
+        <v>587.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1761606.11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5891.66</v>
+      </c>
+      <c r="H7" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J7" t="n">
+        <v>299</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Road + Waterbus</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="D8" t="n">
+        <v>587.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1761606.11</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5891.66</v>
+      </c>
+      <c r="H8" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J8" t="n">
+        <v>299</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Road Only</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="D9" t="n">
+        <v>587.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1761606.11</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5891.66</v>
+      </c>
+      <c r="H9" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>299</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>hub_strategy</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>traffic_condition</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>avg_time_min</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>total_distance_km</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>avg_distance_km</t>
+          <t>total_co2_kg</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>total_cost_vnd</t>
+          <t>avg_cost_vnd</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>avg_cost_vnd</t>
+          <t>multimodal_used_cnt</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_co2_kg</t>
+          <t>time_improvement_pct</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>avg_co2_kg</t>
+          <t>co2_improvement_pct</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>delivery_count</t>
+          <t>cost_improvement_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Off-Peak</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Full Multimodal</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>3.11</v>
-      </c>
       <c r="D2" t="n">
-        <v>272.08</v>
+        <v>3.93</v>
       </c>
       <c r="E2" t="n">
-        <v>1.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>816253.66</v>
+        <v>5891.66</v>
       </c>
       <c r="G2" t="n">
-        <v>4664.31</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>32.65</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Off-Peak</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Road + Metro</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>3.11</v>
-      </c>
       <c r="D3" t="n">
-        <v>272.08</v>
+        <v>3.93</v>
       </c>
       <c r="E3" t="n">
-        <v>1.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>816253.66</v>
+        <v>5891.66</v>
       </c>
       <c r="G3" t="n">
-        <v>4664.31</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>32.65</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Off-Peak</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Road + Waterbus</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>3.11</v>
-      </c>
       <c r="D4" t="n">
-        <v>272.08</v>
+        <v>3.93</v>
       </c>
       <c r="E4" t="n">
-        <v>1.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>816253.66</v>
+        <v>5891.66</v>
       </c>
       <c r="G4" t="n">
-        <v>4664.31</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>32.65</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Off-Peak</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Road Only</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>3.11</v>
-      </c>
       <c r="D5" t="n">
-        <v>272.08</v>
+        <v>3.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>816253.66</v>
+        <v>5891.66</v>
       </c>
       <c r="G5" t="n">
-        <v>4664.31</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>32.65</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Peak</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Full Multimodal</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>7.77</v>
-      </c>
       <c r="D6" t="n">
-        <v>272.08</v>
+        <v>9.82</v>
       </c>
       <c r="E6" t="n">
-        <v>1.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>816253.66</v>
+        <v>5891.66</v>
       </c>
       <c r="G6" t="n">
-        <v>4664.31</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>32.65</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Peak</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Road + Metro</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>7.77</v>
-      </c>
       <c r="D7" t="n">
-        <v>272.08</v>
+        <v>9.82</v>
       </c>
       <c r="E7" t="n">
-        <v>1.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>816253.66</v>
+        <v>5891.66</v>
       </c>
       <c r="G7" t="n">
-        <v>4664.31</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>32.65</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Peak</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Road + Waterbus</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>7.77</v>
-      </c>
       <c r="D8" t="n">
-        <v>272.08</v>
+        <v>9.82</v>
       </c>
       <c r="E8" t="n">
-        <v>1.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>816253.66</v>
+        <v>5891.66</v>
       </c>
       <c r="G8" t="n">
-        <v>4664.31</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>32.65</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Peak</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Road Only</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="E9" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5891.66</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>traffic_condition</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>avg_time_min</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total_distance_km</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>avg_distance_km</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_cost_vnd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>avg_cost_vnd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total_co2_kg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>avg_co2_kg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>delivery_count</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>multimodal_used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Central Full Multimodal</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1832.42</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4161933.71</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13873.11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K2" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Central Road + Metro</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1832.42</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4161933.71</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13873.11</v>
+      </c>
+      <c r="H3" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J3" t="n">
+        <v>300</v>
+      </c>
+      <c r="K3" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Central Road + Waterbus</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1897.84</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5693519.39</v>
+      </c>
+      <c r="G4" t="n">
+        <v>18978.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>227.74</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J4" t="n">
+        <v>300</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Central Road Only</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1897.84</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5693519.39</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18978.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>227.74</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J5" t="n">
+        <v>300</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Central Full Multimodal</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1986.65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4240068.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14133.56</v>
+      </c>
+      <c r="H6" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J6" t="n">
+        <v>300</v>
+      </c>
+      <c r="K6" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Central Road + Metro</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1986.65</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4240068.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14133.56</v>
+      </c>
+      <c r="H7" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J7" t="n">
+        <v>300</v>
+      </c>
+      <c r="K7" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Central Road + Waterbus</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1949.45</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5057029.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16856.77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>181.27</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>300</v>
+      </c>
+      <c r="K8" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Road Only</t>
+          <t>Central Road Only</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.77</v>
+        <v>31.63</v>
       </c>
       <c r="D9" t="n">
-        <v>272.08</v>
+        <v>1897.84</v>
       </c>
       <c r="E9" t="n">
-        <v>1.55</v>
+        <v>6.33</v>
       </c>
       <c r="F9" t="n">
-        <v>816253.66</v>
+        <v>5693519.39</v>
       </c>
       <c r="G9" t="n">
-        <v>4664.31</v>
+        <v>18978.4</v>
       </c>
       <c r="H9" t="n">
-        <v>32.65</v>
+        <v>227.74</v>
       </c>
       <c r="I9" t="n">
-        <v>0.19</v>
+        <v>0.76</v>
       </c>
       <c r="J9" t="n">
-        <v>175</v>
+        <v>300</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>hub_strategy</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>traffic_condition</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_time_min</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>total_co2_kg</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>avg_cost_vnd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>multimodal_used_cnt</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>time_improvement_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>co2_improvement_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>cost_improvement_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>centralized</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Central Full Multimodal</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="E2" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13873.11</v>
+      </c>
+      <c r="G2" t="n">
+        <v>95</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>centralized</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Central Road + Metro</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="E3" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13873.11</v>
+      </c>
+      <c r="G3" t="n">
+        <v>95</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>centralized</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Central Road + Waterbus</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="E4" t="n">
+        <v>227.74</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18978.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>centralized</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Central Road Only</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="E5" t="n">
+        <v>227.74</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18978.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>centralized</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Central Full Multimodal</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="E6" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14133.56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>174</v>
+      </c>
+      <c r="H6" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>centralized</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Central Road + Metro</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14133.56</v>
+      </c>
+      <c r="G7" t="n">
+        <v>174</v>
+      </c>
+      <c r="H7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>centralized</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Central Road + Waterbus</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>181.27</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16856.77</v>
+      </c>
+      <c r="G8" t="n">
+        <v>96</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>centralized</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Central Road Only</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="E9" t="n">
+        <v>227.74</v>
+      </c>
+      <c r="F9" t="n">
+        <v>18978.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_results.xlsx
+++ b/results/summary_results.xlsx
@@ -488,28 +488,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="D2" t="n">
-        <v>587.2</v>
+        <v>271.64</v>
       </c>
       <c r="E2" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="F2" t="n">
-        <v>1761606.11</v>
+        <v>814907.1899999999</v>
       </c>
       <c r="G2" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="H2" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J2" t="n">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>587.2</v>
+        <v>271.64</v>
       </c>
       <c r="E3" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="F3" t="n">
-        <v>1761606.11</v>
+        <v>814907.1899999999</v>
       </c>
       <c r="G3" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="H3" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J3" t="n">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -566,28 +566,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="D4" t="n">
-        <v>587.2</v>
+        <v>271.64</v>
       </c>
       <c r="E4" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="F4" t="n">
-        <v>1761606.11</v>
+        <v>814907.1899999999</v>
       </c>
       <c r="G4" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="H4" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J4" t="n">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -605,28 +605,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="D5" t="n">
-        <v>587.2</v>
+        <v>271.64</v>
       </c>
       <c r="E5" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="F5" t="n">
-        <v>1761606.11</v>
+        <v>814907.1899999999</v>
       </c>
       <c r="G5" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="H5" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J5" t="n">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -644,28 +644,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.82</v>
+        <v>7.76</v>
       </c>
       <c r="D6" t="n">
-        <v>587.2</v>
+        <v>271.64</v>
       </c>
       <c r="E6" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="F6" t="n">
-        <v>1761606.11</v>
+        <v>814907.1899999999</v>
       </c>
       <c r="G6" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="H6" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J6" t="n">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -683,28 +683,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.82</v>
+        <v>7.76</v>
       </c>
       <c r="D7" t="n">
-        <v>587.2</v>
+        <v>271.64</v>
       </c>
       <c r="E7" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="F7" t="n">
-        <v>1761606.11</v>
+        <v>814907.1899999999</v>
       </c>
       <c r="G7" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="H7" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J7" t="n">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.82</v>
+        <v>7.76</v>
       </c>
       <c r="D8" t="n">
-        <v>587.2</v>
+        <v>271.64</v>
       </c>
       <c r="E8" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="F8" t="n">
-        <v>1761606.11</v>
+        <v>814907.1899999999</v>
       </c>
       <c r="G8" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="H8" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="I8" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J8" t="n">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -761,28 +761,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.82</v>
+        <v>7.76</v>
       </c>
       <c r="D9" t="n">
-        <v>587.2</v>
+        <v>271.64</v>
       </c>
       <c r="E9" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="F9" t="n">
-        <v>1761606.11</v>
+        <v>814907.1899999999</v>
       </c>
       <c r="G9" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="H9" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J9" t="n">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="E2" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="F2" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="E3" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="F3" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="E4" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="F4" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="E5" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="F5" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.82</v>
+        <v>7.76</v>
       </c>
       <c r="E6" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="F6" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.82</v>
+        <v>7.76</v>
       </c>
       <c r="E7" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="F7" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.82</v>
+        <v>7.76</v>
       </c>
       <c r="E8" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="F8" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9.82</v>
+        <v>7.76</v>
       </c>
       <c r="E9" t="n">
-        <v>70.45999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="F9" t="n">
-        <v>5891.66</v>
+        <v>4656.61</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1241,31 +1241,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11.72</v>
+        <v>4.99</v>
       </c>
       <c r="D2" t="n">
-        <v>1832.42</v>
+        <v>728.72</v>
       </c>
       <c r="E2" t="n">
-        <v>6.11</v>
+        <v>2.5</v>
       </c>
       <c r="F2" t="n">
-        <v>4161933.71</v>
+        <v>2186154.16</v>
       </c>
       <c r="G2" t="n">
-        <v>13873.11</v>
+        <v>7486.83</v>
       </c>
       <c r="H2" t="n">
-        <v>127.65</v>
+        <v>87.44</v>
       </c>
       <c r="I2" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="J2" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K2" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1280,31 +1280,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.72</v>
+        <v>4.99</v>
       </c>
       <c r="D3" t="n">
-        <v>1832.42</v>
+        <v>728.72</v>
       </c>
       <c r="E3" t="n">
-        <v>6.11</v>
+        <v>2.5</v>
       </c>
       <c r="F3" t="n">
-        <v>4161933.71</v>
+        <v>2186154.16</v>
       </c>
       <c r="G3" t="n">
-        <v>13873.11</v>
+        <v>7486.83</v>
       </c>
       <c r="H3" t="n">
-        <v>127.65</v>
+        <v>87.44</v>
       </c>
       <c r="I3" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="J3" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K3" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1319,28 +1319,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12.65</v>
+        <v>4.99</v>
       </c>
       <c r="D4" t="n">
-        <v>1897.84</v>
+        <v>728.72</v>
       </c>
       <c r="E4" t="n">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="F4" t="n">
-        <v>5693519.39</v>
+        <v>2186154.16</v>
       </c>
       <c r="G4" t="n">
-        <v>18978.4</v>
+        <v>7486.83</v>
       </c>
       <c r="H4" t="n">
-        <v>227.74</v>
+        <v>87.44</v>
       </c>
       <c r="I4" t="n">
-        <v>0.76</v>
+        <v>0.3</v>
       </c>
       <c r="J4" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1358,28 +1358,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.65</v>
+        <v>4.99</v>
       </c>
       <c r="D5" t="n">
-        <v>1897.84</v>
+        <v>728.72</v>
       </c>
       <c r="E5" t="n">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="F5" t="n">
-        <v>5693519.39</v>
+        <v>2186154.16</v>
       </c>
       <c r="G5" t="n">
-        <v>18978.4</v>
+        <v>7486.83</v>
       </c>
       <c r="H5" t="n">
-        <v>227.74</v>
+        <v>87.44</v>
       </c>
       <c r="I5" t="n">
-        <v>0.76</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1397,31 +1397,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.16</v>
+        <v>11.3</v>
       </c>
       <c r="D6" t="n">
-        <v>1986.65</v>
+        <v>737.11</v>
       </c>
       <c r="E6" t="n">
-        <v>6.62</v>
+        <v>2.52</v>
       </c>
       <c r="F6" t="n">
-        <v>4240068.04</v>
+        <v>3352809.12</v>
       </c>
       <c r="G6" t="n">
-        <v>14133.56</v>
+        <v>11482.22</v>
       </c>
       <c r="H6" t="n">
-        <v>93.65000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="J6" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K6" t="n">
-        <v>174</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -1436,31 +1436,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.16</v>
+        <v>11.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1986.65</v>
+        <v>737.11</v>
       </c>
       <c r="E7" t="n">
-        <v>6.62</v>
+        <v>2.52</v>
       </c>
       <c r="F7" t="n">
-        <v>4240068.04</v>
+        <v>3352809.12</v>
       </c>
       <c r="G7" t="n">
-        <v>14133.56</v>
+        <v>11482.22</v>
       </c>
       <c r="H7" t="n">
-        <v>93.65000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="J7" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K7" t="n">
-        <v>174</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
@@ -1475,31 +1475,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.17</v>
+        <v>12.48</v>
       </c>
       <c r="D8" t="n">
-        <v>1949.45</v>
+        <v>728.72</v>
       </c>
       <c r="E8" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F8" t="n">
-        <v>5057029.9</v>
+        <v>2186154.16</v>
       </c>
       <c r="G8" t="n">
-        <v>16856.77</v>
+        <v>7486.83</v>
       </c>
       <c r="H8" t="n">
-        <v>181.27</v>
+        <v>87.44</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K8" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1514,28 +1514,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.63</v>
+        <v>12.48</v>
       </c>
       <c r="D9" t="n">
-        <v>1897.84</v>
+        <v>728.72</v>
       </c>
       <c r="E9" t="n">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="F9" t="n">
-        <v>5693519.39</v>
+        <v>2186154.16</v>
       </c>
       <c r="G9" t="n">
-        <v>18978.4</v>
+        <v>7486.83</v>
       </c>
       <c r="H9" t="n">
-        <v>227.74</v>
+        <v>87.44</v>
       </c>
       <c r="I9" t="n">
-        <v>0.76</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.72</v>
+        <v>4.99</v>
       </c>
       <c r="E2" t="n">
-        <v>127.65</v>
+        <v>87.44</v>
       </c>
       <c r="F2" t="n">
-        <v>13873.11</v>
+        <v>7486.83</v>
       </c>
       <c r="G2" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>43.9</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>26.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1662,25 +1662,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.72</v>
+        <v>4.99</v>
       </c>
       <c r="E3" t="n">
-        <v>127.65</v>
+        <v>87.44</v>
       </c>
       <c r="F3" t="n">
-        <v>13873.11</v>
+        <v>7486.83</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>43.9</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>26.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.65</v>
+        <v>4.99</v>
       </c>
       <c r="E4" t="n">
-        <v>227.74</v>
+        <v>87.44</v>
       </c>
       <c r="F4" t="n">
-        <v>18978.4</v>
+        <v>7486.83</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.65</v>
+        <v>4.99</v>
       </c>
       <c r="E5" t="n">
-        <v>227.74</v>
+        <v>87.44</v>
       </c>
       <c r="F5" t="n">
-        <v>18978.4</v>
+        <v>7486.83</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.16</v>
+        <v>11.3</v>
       </c>
       <c r="E6" t="n">
-        <v>93.65000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>14133.56</v>
+        <v>11482.22</v>
       </c>
       <c r="G6" t="n">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="H6" t="n">
-        <v>42.6</v>
+        <v>9.5</v>
       </c>
       <c r="I6" t="n">
-        <v>58.9</v>
+        <v>26.1</v>
       </c>
       <c r="J6" t="n">
-        <v>25.5</v>
+        <v>-53.4</v>
       </c>
     </row>
     <row r="7">
@@ -1814,25 +1814,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.16</v>
+        <v>11.3</v>
       </c>
       <c r="E7" t="n">
-        <v>93.65000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>14133.56</v>
+        <v>11482.22</v>
       </c>
       <c r="G7" t="n">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="H7" t="n">
-        <v>42.6</v>
+        <v>9.5</v>
       </c>
       <c r="I7" t="n">
-        <v>58.9</v>
+        <v>26.1</v>
       </c>
       <c r="J7" t="n">
-        <v>25.5</v>
+        <v>-53.4</v>
       </c>
     </row>
     <row r="8">
@@ -1852,25 +1852,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.17</v>
+        <v>12.48</v>
       </c>
       <c r="E8" t="n">
-        <v>181.27</v>
+        <v>87.44</v>
       </c>
       <c r="F8" t="n">
-        <v>16856.77</v>
+        <v>7486.83</v>
       </c>
       <c r="G8" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1890,13 +1890,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31.63</v>
+        <v>12.48</v>
       </c>
       <c r="E9" t="n">
-        <v>227.74</v>
+        <v>87.44</v>
       </c>
       <c r="F9" t="n">
-        <v>18978.4</v>
+        <v>7486.83</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>

--- a/results/summary_results.xlsx
+++ b/results/summary_results.xlsx
@@ -488,28 +488,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="D2" t="n">
-        <v>271.64</v>
+        <v>331.41</v>
       </c>
       <c r="E2" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="F2" t="n">
-        <v>814907.1899999999</v>
+        <v>994233.6</v>
       </c>
       <c r="G2" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="H2" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="I2" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="J2" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="D3" t="n">
-        <v>271.64</v>
+        <v>331.41</v>
       </c>
       <c r="E3" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="F3" t="n">
-        <v>814907.1899999999</v>
+        <v>994233.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="H3" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="I3" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -566,28 +566,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="D4" t="n">
-        <v>271.64</v>
+        <v>331.41</v>
       </c>
       <c r="E4" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="F4" t="n">
-        <v>814907.1899999999</v>
+        <v>994233.6</v>
       </c>
       <c r="G4" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="H4" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="I4" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -605,28 +605,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="D5" t="n">
-        <v>271.64</v>
+        <v>331.41</v>
       </c>
       <c r="E5" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="F5" t="n">
-        <v>814907.1899999999</v>
+        <v>994233.6</v>
       </c>
       <c r="G5" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="H5" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="I5" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -644,28 +644,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.76</v>
+        <v>5.66</v>
       </c>
       <c r="D6" t="n">
-        <v>271.64</v>
+        <v>331.41</v>
       </c>
       <c r="E6" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="F6" t="n">
-        <v>814907.1899999999</v>
+        <v>994233.6</v>
       </c>
       <c r="G6" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="H6" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="I6" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -683,28 +683,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.76</v>
+        <v>5.66</v>
       </c>
       <c r="D7" t="n">
-        <v>271.64</v>
+        <v>331.41</v>
       </c>
       <c r="E7" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="F7" t="n">
-        <v>814907.1899999999</v>
+        <v>994233.6</v>
       </c>
       <c r="G7" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="H7" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="I7" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="J7" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.76</v>
+        <v>5.66</v>
       </c>
       <c r="D8" t="n">
-        <v>271.64</v>
+        <v>331.41</v>
       </c>
       <c r="E8" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="F8" t="n">
-        <v>814907.1899999999</v>
+        <v>994233.6</v>
       </c>
       <c r="G8" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="H8" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="I8" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -761,28 +761,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.76</v>
+        <v>5.66</v>
       </c>
       <c r="D9" t="n">
-        <v>271.64</v>
+        <v>331.41</v>
       </c>
       <c r="E9" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="F9" t="n">
-        <v>814907.1899999999</v>
+        <v>994233.6</v>
       </c>
       <c r="G9" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="H9" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="I9" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="E2" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="F2" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="E3" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="F3" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="E4" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="F4" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="E5" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="F5" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.76</v>
+        <v>5.66</v>
       </c>
       <c r="E6" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="F6" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7.76</v>
+        <v>5.66</v>
       </c>
       <c r="E7" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="F7" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.76</v>
+        <v>5.66</v>
       </c>
       <c r="E8" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="F8" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.76</v>
+        <v>5.66</v>
       </c>
       <c r="E9" t="n">
-        <v>32.6</v>
+        <v>39.77</v>
       </c>
       <c r="F9" t="n">
-        <v>4656.61</v>
+        <v>3393.29</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1244,25 +1244,25 @@
         <v>4.99</v>
       </c>
       <c r="D2" t="n">
-        <v>728.72</v>
+        <v>736.26</v>
       </c>
       <c r="E2" t="n">
         <v>2.5</v>
       </c>
       <c r="F2" t="n">
-        <v>2186154.16</v>
+        <v>2208772.39</v>
       </c>
       <c r="G2" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="H2" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>0.3</v>
       </c>
       <c r="J2" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1283,25 +1283,25 @@
         <v>4.99</v>
       </c>
       <c r="D3" t="n">
-        <v>728.72</v>
+        <v>736.26</v>
       </c>
       <c r="E3" t="n">
         <v>2.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2186154.16</v>
+        <v>2208772.39</v>
       </c>
       <c r="G3" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="H3" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0.3</v>
       </c>
       <c r="J3" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1322,25 +1322,25 @@
         <v>4.99</v>
       </c>
       <c r="D4" t="n">
-        <v>728.72</v>
+        <v>736.26</v>
       </c>
       <c r="E4" t="n">
         <v>2.5</v>
       </c>
       <c r="F4" t="n">
-        <v>2186154.16</v>
+        <v>2208772.39</v>
       </c>
       <c r="G4" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="H4" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>0.3</v>
       </c>
       <c r="J4" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1361,25 +1361,25 @@
         <v>4.99</v>
       </c>
       <c r="D5" t="n">
-        <v>728.72</v>
+        <v>736.26</v>
       </c>
       <c r="E5" t="n">
         <v>2.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2186154.16</v>
+        <v>2208772.39</v>
       </c>
       <c r="G5" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="H5" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0.3</v>
       </c>
       <c r="J5" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1397,31 +1397,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.3</v>
+        <v>11.29</v>
       </c>
       <c r="D6" t="n">
-        <v>737.11</v>
+        <v>744.78</v>
       </c>
       <c r="E6" t="n">
         <v>2.52</v>
       </c>
       <c r="F6" t="n">
-        <v>3352809.12</v>
+        <v>3394397.34</v>
       </c>
       <c r="G6" t="n">
-        <v>11482.22</v>
+        <v>11506.43</v>
       </c>
       <c r="H6" t="n">
-        <v>64.65000000000001</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0.22</v>
       </c>
       <c r="J6" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K6" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7">
@@ -1436,31 +1436,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11.3</v>
+        <v>11.29</v>
       </c>
       <c r="D7" t="n">
-        <v>737.11</v>
+        <v>744.78</v>
       </c>
       <c r="E7" t="n">
         <v>2.52</v>
       </c>
       <c r="F7" t="n">
-        <v>3352809.12</v>
+        <v>3394397.34</v>
       </c>
       <c r="G7" t="n">
-        <v>11482.22</v>
+        <v>11506.43</v>
       </c>
       <c r="H7" t="n">
-        <v>64.65000000000001</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>0.22</v>
       </c>
       <c r="J7" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
@@ -1478,25 +1478,25 @@
         <v>12.48</v>
       </c>
       <c r="D8" t="n">
-        <v>728.72</v>
+        <v>736.26</v>
       </c>
       <c r="E8" t="n">
         <v>2.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2186154.16</v>
+        <v>2208772.39</v>
       </c>
       <c r="G8" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="H8" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>0.3</v>
       </c>
       <c r="J8" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1517,25 +1517,25 @@
         <v>12.48</v>
       </c>
       <c r="D9" t="n">
-        <v>728.72</v>
+        <v>736.26</v>
       </c>
       <c r="E9" t="n">
         <v>2.5</v>
       </c>
       <c r="F9" t="n">
-        <v>2186154.16</v>
+        <v>2208772.39</v>
       </c>
       <c r="G9" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="H9" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="I9" t="n">
         <v>0.3</v>
       </c>
       <c r="J9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1627,10 +1627,10 @@
         <v>4.99</v>
       </c>
       <c r="E2" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1665,10 +1665,10 @@
         <v>4.99</v>
       </c>
       <c r="E3" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1703,10 +1703,10 @@
         <v>4.99</v>
       </c>
       <c r="E4" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1741,10 +1741,10 @@
         <v>4.99</v>
       </c>
       <c r="E5" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.3</v>
+        <v>11.29</v>
       </c>
       <c r="E6" t="n">
-        <v>64.65000000000001</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>11482.22</v>
+        <v>11506.43</v>
       </c>
       <c r="G6" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H6" t="n">
         <v>9.5</v>
       </c>
       <c r="I6" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="J6" t="n">
-        <v>-53.4</v>
+        <v>-53.7</v>
       </c>
     </row>
     <row r="7">
@@ -1814,25 +1814,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.3</v>
+        <v>11.29</v>
       </c>
       <c r="E7" t="n">
-        <v>64.65000000000001</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>11482.22</v>
+        <v>11506.43</v>
       </c>
       <c r="G7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H7" t="n">
         <v>9.5</v>
       </c>
       <c r="I7" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="J7" t="n">
-        <v>-53.4</v>
+        <v>-53.7</v>
       </c>
     </row>
     <row r="8">
@@ -1855,10 +1855,10 @@
         <v>12.48</v>
       </c>
       <c r="E8" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1893,10 +1893,10 @@
         <v>12.48</v>
       </c>
       <c r="E9" t="n">
-        <v>87.44</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>7486.83</v>
+        <v>7487.36</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>

--- a/results/summary_results.xlsx
+++ b/results/summary_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KPI_nearest" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Improve_nearest" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="KPI_centralized" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Improve_centralized" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_nearest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improve_nearest" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_centralized" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improve_centralized" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,25 +488,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="D2" t="n">
-        <v>271.64</v>
+        <v>301.31</v>
       </c>
       <c r="E2" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="F2" t="n">
-        <v>814907.1899999999</v>
+        <v>903920.67</v>
       </c>
       <c r="G2" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="H2" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J2" t="n">
         <v>175</v>
@@ -527,25 +527,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="D3" t="n">
-        <v>271.64</v>
+        <v>301.31</v>
       </c>
       <c r="E3" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="F3" t="n">
-        <v>814907.1899999999</v>
+        <v>903920.67</v>
       </c>
       <c r="G3" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="H3" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J3" t="n">
         <v>175</v>
@@ -566,25 +566,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="D4" t="n">
-        <v>271.64</v>
+        <v>301.31</v>
       </c>
       <c r="E4" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="F4" t="n">
-        <v>814907.1899999999</v>
+        <v>903920.67</v>
       </c>
       <c r="G4" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="H4" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J4" t="n">
         <v>175</v>
@@ -605,25 +605,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="D5" t="n">
-        <v>271.64</v>
+        <v>301.31</v>
       </c>
       <c r="E5" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="F5" t="n">
-        <v>814907.1899999999</v>
+        <v>903920.67</v>
       </c>
       <c r="G5" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="H5" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J5" t="n">
         <v>175</v>
@@ -644,25 +644,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>271.64</v>
+        <v>301.31</v>
       </c>
       <c r="E6" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="F6" t="n">
-        <v>814907.1899999999</v>
+        <v>903920.67</v>
       </c>
       <c r="G6" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="H6" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J6" t="n">
         <v>175</v>
@@ -683,25 +683,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>271.64</v>
+        <v>301.31</v>
       </c>
       <c r="E7" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="F7" t="n">
-        <v>814907.1899999999</v>
+        <v>903920.67</v>
       </c>
       <c r="G7" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="H7" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J7" t="n">
         <v>175</v>
@@ -722,25 +722,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>271.64</v>
+        <v>301.31</v>
       </c>
       <c r="E8" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="F8" t="n">
-        <v>814907.1899999999</v>
+        <v>903920.67</v>
       </c>
       <c r="G8" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="H8" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J8" t="n">
         <v>175</v>
@@ -761,25 +761,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>271.64</v>
+        <v>301.31</v>
       </c>
       <c r="E9" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="F9" t="n">
-        <v>814907.1899999999</v>
+        <v>903920.67</v>
       </c>
       <c r="G9" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="H9" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="J9" t="n">
         <v>175</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="E2" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="F2" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="E3" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="F3" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="E4" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="F4" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="E5" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="F5" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="F6" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="F7" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="F8" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.76</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>32.6</v>
+        <v>36.16</v>
       </c>
       <c r="F9" t="n">
-        <v>4656.61</v>
+        <v>5165.26</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1241,28 +1241,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.99</v>
+        <v>4.01</v>
       </c>
       <c r="D2" t="n">
-        <v>728.72</v>
+        <v>583.75</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="F2" t="n">
-        <v>2186154.16</v>
+        <v>1751264.21</v>
       </c>
       <c r="G2" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="H2" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="J2" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1280,28 +1280,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.99</v>
+        <v>4.01</v>
       </c>
       <c r="D3" t="n">
-        <v>728.72</v>
+        <v>583.75</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="F3" t="n">
-        <v>2186154.16</v>
+        <v>1751264.21</v>
       </c>
       <c r="G3" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="H3" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="J3" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1319,28 +1319,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.99</v>
+        <v>4.01</v>
       </c>
       <c r="D4" t="n">
-        <v>728.72</v>
+        <v>583.75</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="F4" t="n">
-        <v>2186154.16</v>
+        <v>1751264.21</v>
       </c>
       <c r="G4" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="H4" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="J4" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1358,28 +1358,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.99</v>
+        <v>4.01</v>
       </c>
       <c r="D5" t="n">
-        <v>728.72</v>
+        <v>583.75</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="F5" t="n">
-        <v>2186154.16</v>
+        <v>1751264.21</v>
       </c>
       <c r="G5" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="H5" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="J5" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1397,31 +1397,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.3</v>
+        <v>10.03</v>
       </c>
       <c r="D6" t="n">
-        <v>737.11</v>
+        <v>583.75</v>
       </c>
       <c r="E6" t="n">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
       <c r="F6" t="n">
-        <v>3352809.12</v>
+        <v>1751264.21</v>
       </c>
       <c r="G6" t="n">
-        <v>11482.22</v>
+        <v>6018.09</v>
       </c>
       <c r="H6" t="n">
-        <v>64.65000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="J6" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K6" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1436,31 +1436,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11.3</v>
+        <v>10.03</v>
       </c>
       <c r="D7" t="n">
-        <v>737.11</v>
+        <v>583.75</v>
       </c>
       <c r="E7" t="n">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
       <c r="F7" t="n">
-        <v>3352809.12</v>
+        <v>1751264.21</v>
       </c>
       <c r="G7" t="n">
-        <v>11482.22</v>
+        <v>6018.09</v>
       </c>
       <c r="H7" t="n">
-        <v>64.65000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="J7" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K7" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1475,28 +1475,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.48</v>
+        <v>10.03</v>
       </c>
       <c r="D8" t="n">
-        <v>728.72</v>
+        <v>583.75</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="F8" t="n">
-        <v>2186154.16</v>
+        <v>1751264.21</v>
       </c>
       <c r="G8" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="H8" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="J8" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1514,28 +1514,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.48</v>
+        <v>10.03</v>
       </c>
       <c r="D9" t="n">
-        <v>728.72</v>
+        <v>583.75</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="F9" t="n">
-        <v>2186154.16</v>
+        <v>1751264.21</v>
       </c>
       <c r="G9" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="H9" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="J9" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.99</v>
+        <v>4.01</v>
       </c>
       <c r="E2" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="F2" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.99</v>
+        <v>4.01</v>
       </c>
       <c r="E3" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="F3" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.99</v>
+        <v>4.01</v>
       </c>
       <c r="E4" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="F4" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.99</v>
+        <v>4.01</v>
       </c>
       <c r="E5" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="F5" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.3</v>
+        <v>10.03</v>
       </c>
       <c r="E6" t="n">
-        <v>64.65000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="F6" t="n">
-        <v>11482.22</v>
+        <v>6018.09</v>
       </c>
       <c r="G6" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-53.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1814,25 +1814,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.3</v>
+        <v>10.03</v>
       </c>
       <c r="E7" t="n">
-        <v>64.65000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="F7" t="n">
-        <v>11482.22</v>
+        <v>6018.09</v>
       </c>
       <c r="G7" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-53.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.48</v>
+        <v>10.03</v>
       </c>
       <c r="E8" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="F8" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1890,13 +1890,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.48</v>
+        <v>10.03</v>
       </c>
       <c r="E9" t="n">
-        <v>87.44</v>
+        <v>70.05</v>
       </c>
       <c r="F9" t="n">
-        <v>7486.83</v>
+        <v>6018.09</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>

--- a/results/summary_results.xlsx
+++ b/results/summary_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_nearest" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improve_nearest" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_centralized" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improve_centralized" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="KPI_nearest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Improve_nearest" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="KPI_centralized" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Improve_centralized" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,28 +488,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.44</v>
+        <v>5.66</v>
       </c>
       <c r="D2" t="n">
-        <v>301.31</v>
+        <v>497.89</v>
       </c>
       <c r="E2" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="F2" t="n">
-        <v>903920.67</v>
+        <v>1493661.37</v>
       </c>
       <c r="G2" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="J2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.44</v>
+        <v>5.66</v>
       </c>
       <c r="D3" t="n">
-        <v>301.31</v>
+        <v>497.89</v>
       </c>
       <c r="E3" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="F3" t="n">
-        <v>903920.67</v>
+        <v>1493661.37</v>
       </c>
       <c r="G3" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="I3" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="J3" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -566,28 +566,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.44</v>
+        <v>5.66</v>
       </c>
       <c r="D4" t="n">
-        <v>301.31</v>
+        <v>497.89</v>
       </c>
       <c r="E4" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="F4" t="n">
-        <v>903920.67</v>
+        <v>1493661.37</v>
       </c>
       <c r="G4" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="I4" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="J4" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -605,28 +605,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.44</v>
+        <v>5.66</v>
       </c>
       <c r="D5" t="n">
-        <v>301.31</v>
+        <v>497.89</v>
       </c>
       <c r="E5" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="F5" t="n">
-        <v>903920.67</v>
+        <v>1493661.37</v>
       </c>
       <c r="G5" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="I5" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="J5" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -644,31 +644,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.609999999999999</v>
+        <v>14.03</v>
       </c>
       <c r="D6" t="n">
-        <v>301.31</v>
+        <v>502.09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.72</v>
+        <v>2.85</v>
       </c>
       <c r="F6" t="n">
-        <v>903920.67</v>
+        <v>1626918.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5165.26</v>
+        <v>9243.860000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>36.16</v>
+        <v>57.74</v>
       </c>
       <c r="I6" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="J6" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -683,31 +683,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.609999999999999</v>
+        <v>14.03</v>
       </c>
       <c r="D7" t="n">
-        <v>301.31</v>
+        <v>502.09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.72</v>
+        <v>2.85</v>
       </c>
       <c r="F7" t="n">
-        <v>903920.67</v>
+        <v>1626918.7</v>
       </c>
       <c r="G7" t="n">
-        <v>5165.26</v>
+        <v>9243.860000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>36.16</v>
+        <v>57.74</v>
       </c>
       <c r="I7" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="J7" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.609999999999999</v>
+        <v>14.14</v>
       </c>
       <c r="D8" t="n">
-        <v>301.31</v>
+        <v>497.89</v>
       </c>
       <c r="E8" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="F8" t="n">
-        <v>903920.67</v>
+        <v>1493661.37</v>
       </c>
       <c r="G8" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="I8" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="J8" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -761,28 +761,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.609999999999999</v>
+        <v>14.14</v>
       </c>
       <c r="D9" t="n">
-        <v>301.31</v>
+        <v>497.89</v>
       </c>
       <c r="E9" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="F9" t="n">
-        <v>903920.67</v>
+        <v>1493661.37</v>
       </c>
       <c r="G9" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="J9" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.44</v>
+        <v>5.66</v>
       </c>
       <c r="E2" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="F2" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.44</v>
+        <v>5.66</v>
       </c>
       <c r="E3" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="F3" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.44</v>
+        <v>5.66</v>
       </c>
       <c r="E4" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="F4" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.44</v>
+        <v>5.66</v>
       </c>
       <c r="E5" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="F5" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1023,25 +1023,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8.609999999999999</v>
+        <v>14.03</v>
       </c>
       <c r="E6" t="n">
-        <v>36.16</v>
+        <v>57.74</v>
       </c>
       <c r="F6" t="n">
-        <v>5165.26</v>
+        <v>9243.860000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="7">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8.609999999999999</v>
+        <v>14.03</v>
       </c>
       <c r="E7" t="n">
-        <v>36.16</v>
+        <v>57.74</v>
       </c>
       <c r="F7" t="n">
-        <v>5165.26</v>
+        <v>9243.860000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="8">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.609999999999999</v>
+        <v>14.14</v>
       </c>
       <c r="E8" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="F8" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.609999999999999</v>
+        <v>14.14</v>
       </c>
       <c r="E9" t="n">
-        <v>36.16</v>
+        <v>59.75</v>
       </c>
       <c r="F9" t="n">
-        <v>5165.26</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1241,28 +1241,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.01</v>
+        <v>5.66</v>
       </c>
       <c r="D2" t="n">
-        <v>583.75</v>
+        <v>497.89</v>
       </c>
       <c r="E2" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="F2" t="n">
-        <v>1751264.21</v>
+        <v>1493661.37</v>
       </c>
       <c r="G2" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="J2" t="n">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1280,28 +1280,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.01</v>
+        <v>5.66</v>
       </c>
       <c r="D3" t="n">
-        <v>583.75</v>
+        <v>497.89</v>
       </c>
       <c r="E3" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="F3" t="n">
-        <v>1751264.21</v>
+        <v>1493661.37</v>
       </c>
       <c r="G3" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="I3" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="J3" t="n">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1319,28 +1319,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.01</v>
+        <v>5.66</v>
       </c>
       <c r="D4" t="n">
-        <v>583.75</v>
+        <v>497.89</v>
       </c>
       <c r="E4" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="F4" t="n">
-        <v>1751264.21</v>
+        <v>1493661.37</v>
       </c>
       <c r="G4" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="I4" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="J4" t="n">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1358,28 +1358,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.01</v>
+        <v>5.66</v>
       </c>
       <c r="D5" t="n">
-        <v>583.75</v>
+        <v>497.89</v>
       </c>
       <c r="E5" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="F5" t="n">
-        <v>1751264.21</v>
+        <v>1493661.37</v>
       </c>
       <c r="G5" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="I5" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="J5" t="n">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1397,31 +1397,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10.03</v>
+        <v>14.03</v>
       </c>
       <c r="D6" t="n">
-        <v>583.75</v>
+        <v>502.09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.01</v>
+        <v>2.85</v>
       </c>
       <c r="F6" t="n">
-        <v>1751264.21</v>
+        <v>1626918.7</v>
       </c>
       <c r="G6" t="n">
-        <v>6018.09</v>
+        <v>9243.860000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>70.05</v>
+        <v>57.74</v>
       </c>
       <c r="I6" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="J6" t="n">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -1436,31 +1436,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.03</v>
+        <v>14.03</v>
       </c>
       <c r="D7" t="n">
-        <v>583.75</v>
+        <v>502.09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.01</v>
+        <v>2.85</v>
       </c>
       <c r="F7" t="n">
-        <v>1751264.21</v>
+        <v>1626918.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6018.09</v>
+        <v>9243.860000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>70.05</v>
+        <v>57.74</v>
       </c>
       <c r="I7" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="J7" t="n">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1475,28 +1475,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.03</v>
+        <v>14.14</v>
       </c>
       <c r="D8" t="n">
-        <v>583.75</v>
+        <v>497.89</v>
       </c>
       <c r="E8" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="F8" t="n">
-        <v>1751264.21</v>
+        <v>1493661.37</v>
       </c>
       <c r="G8" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="I8" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="J8" t="n">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1514,28 +1514,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10.03</v>
+        <v>14.14</v>
       </c>
       <c r="D9" t="n">
-        <v>583.75</v>
+        <v>497.89</v>
       </c>
       <c r="E9" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="F9" t="n">
-        <v>1751264.21</v>
+        <v>1493661.37</v>
       </c>
       <c r="G9" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="J9" t="n">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.01</v>
+        <v>5.66</v>
       </c>
       <c r="E2" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="F2" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.01</v>
+        <v>5.66</v>
       </c>
       <c r="E3" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="F3" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.01</v>
+        <v>5.66</v>
       </c>
       <c r="E4" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="F4" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.01</v>
+        <v>5.66</v>
       </c>
       <c r="E5" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="F5" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.03</v>
+        <v>14.03</v>
       </c>
       <c r="E6" t="n">
-        <v>70.05</v>
+        <v>57.74</v>
       </c>
       <c r="F6" t="n">
-        <v>6018.09</v>
+        <v>9243.860000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="7">
@@ -1814,25 +1814,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.03</v>
+        <v>14.03</v>
       </c>
       <c r="E7" t="n">
-        <v>70.05</v>
+        <v>57.74</v>
       </c>
       <c r="F7" t="n">
-        <v>6018.09</v>
+        <v>9243.860000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="8">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.03</v>
+        <v>14.14</v>
       </c>
       <c r="E8" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="F8" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1890,13 +1890,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.03</v>
+        <v>14.14</v>
       </c>
       <c r="E9" t="n">
-        <v>70.05</v>
+        <v>59.75</v>
       </c>
       <c r="F9" t="n">
-        <v>6018.09</v>
+        <v>8486.709999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
